--- a/FischerTropsch_Paper_Michi/Höchst_FischerTropsch_2_Naphta_Brownfield_MH/Datenbank.xlsx
+++ b/FischerTropsch_Paper_Michi/Höchst_FischerTropsch_2_Naphta_Brownfield_MH/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\FischerTropsch_Paper_Michi\Höchst_FischerTropsch_2_Naphta_Brownfield_MH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7567C75-6E29-4701-9471-176D5CFF8375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390B4ACA-1ED3-4DDB-895C-42C023511A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6885" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1568,7 +1568,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1603,56 +1603,64 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1663,80 +1671,12 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -2233,1248 +2173,1248 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="52" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="65" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="59" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="52" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="52" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="52" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="52" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="52" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="52" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="52"/>
+    <col min="1" max="1" width="10.90625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="29" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="65"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="G1" s="29"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="68">
+      <c r="E2" s="7">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="69"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="38"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="8">
         <v>50</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="69"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="38"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="9">
         <v>1500</v>
       </c>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="69"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="52" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="38"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="10">
         <v>0.03</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="69"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="38"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="60">
+      <c r="E6" s="11">
         <v>20</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="69"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="38"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="10">
         <v>0.08</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="69"/>
-      <c r="B8" s="49" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="38"/>
+      <c r="B8" s="48" t="s">
         <v>330</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="E8" s="71">
+      <c r="E8" s="27">
         <v>3.38</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="12" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="69"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="52" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="38"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="8">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="52" t="s">
+      <c r="F9" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="69"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="52" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="38"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="8">
         <v>18520</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="8" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="69"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="52" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="38"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="10">
         <v>0.03</v>
       </c>
-      <c r="F11" s="52" t="s">
+      <c r="F11" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="69"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="52" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="38"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="8">
         <v>0.62</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="69"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="52" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="38"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="8">
         <v>4.43</v>
       </c>
-      <c r="F13" s="52" t="s">
+      <c r="F13" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="69"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="52" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="38"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="8">
         <v>0.41</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="69"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="38"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="11">
         <v>20</v>
       </c>
-      <c r="F15" s="52" t="s">
+      <c r="F15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="55" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="38"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="14">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F16" s="55" t="s">
+      <c r="F16" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="69"/>
-      <c r="B17" s="49" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="38"/>
+      <c r="B17" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="E17" s="72">
+      <c r="E17" s="16">
         <v>3.7</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="69"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="38"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="52" t="s">
+      <c r="D18" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E18" s="59">
+      <c r="E18" s="10">
         <v>0.27</v>
       </c>
-      <c r="F18" s="52" t="s">
+      <c r="F18" s="2" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="69"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="38"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="52" t="s">
+      <c r="D19" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E19" s="59">
+      <c r="E19" s="10">
         <v>700</v>
       </c>
-      <c r="F19" s="52" t="s">
+      <c r="F19" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="69"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="52" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="38"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E20" s="10">
         <v>0.02</v>
       </c>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="69"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="52" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="38"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="52" t="s">
+      <c r="D21" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E21" s="59">
+      <c r="E21" s="10">
         <v>20</v>
       </c>
-      <c r="F21" s="52" t="s">
+      <c r="F21" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="69"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="55" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="38"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="14">
         <v>0.05</v>
       </c>
-      <c r="F22" s="55" t="s">
+      <c r="F22" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="69"/>
-      <c r="B23" s="56" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="38"/>
+      <c r="B23" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E23" s="8">
         <v>0.5</v>
       </c>
-      <c r="F23" s="52" t="s">
+      <c r="F23" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="69"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="52" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="38"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E24" s="53">
+      <c r="E24" s="8">
         <v>1.75</v>
       </c>
-      <c r="F24" s="52" t="s">
+      <c r="F24" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="69"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="52" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="38"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="D25" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="8">
         <v>7000</v>
       </c>
-      <c r="F25" s="52" t="s">
+      <c r="F25" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="69"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="52" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="38"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="52" t="s">
+      <c r="D26" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E26" s="59">
+      <c r="E26" s="10">
         <v>0.05</v>
       </c>
-      <c r="F26" s="52" t="s">
+      <c r="F26" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="69"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="52" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="38"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="52" t="s">
+      <c r="D27" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E27" s="60">
+      <c r="E27" s="11">
         <v>15</v>
       </c>
-      <c r="F27" s="52" t="s">
+      <c r="F27" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="69"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="52" t="s">
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="38"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="52" t="s">
+      <c r="D28" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E28" s="59">
+      <c r="E28" s="10">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F28" s="52" t="s">
+      <c r="F28" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="66" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="58">
+      <c r="E29" s="15">
         <v>490</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="69"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="52" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="38"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="59">
+      <c r="E30" s="10">
         <v>0.01</v>
       </c>
-      <c r="F30" s="52" t="s">
+      <c r="F30" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="69"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="52" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="38"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="60">
+      <c r="E31" s="11">
         <v>20</v>
       </c>
-      <c r="F31" s="52" t="s">
+      <c r="F31" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="69"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="52" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="38"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="52" t="s">
+      <c r="D32" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="74">
+      <c r="E32" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F32" s="52" t="s">
+      <c r="F32" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="69"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="52" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="38"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D33" s="52" t="s">
+      <c r="D33" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="59">
+      <c r="E33" s="10">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F33" s="52" t="s">
+      <c r="F33" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="69"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="52" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="38"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="52" t="s">
+      <c r="D34" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="59">
+      <c r="E34" s="10">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F34" s="52" t="s">
+      <c r="F34" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="69"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="52" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="38"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="52" t="s">
+      <c r="D35" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="59">
+      <c r="E35" s="10">
         <v>0.05</v>
       </c>
-      <c r="F35" s="52" t="s">
+      <c r="F35" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="69"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="55" t="s">
+    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="38"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D36" s="55" t="s">
+      <c r="D36" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="61">
+      <c r="E36" s="14">
         <v>0</v>
       </c>
-      <c r="F36" s="55" t="s">
+      <c r="F36" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="69"/>
-      <c r="B37" s="76" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="38"/>
+      <c r="B37" s="43" t="s">
         <v>305</v>
       </c>
-      <c r="C37" s="57" t="s">
+      <c r="C37" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E37" s="58">
+      <c r="E37" s="15">
         <v>2.83</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="3" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="69"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="52" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="38"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D38" s="52" t="s">
+      <c r="D38" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E38" s="59">
+      <c r="E38" s="10">
         <v>0.03</v>
       </c>
-      <c r="F38" s="52" t="s">
+      <c r="F38" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="69"/>
-      <c r="B39" s="56"/>
-      <c r="C39" s="52" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="38"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="52" t="s">
+      <c r="D39" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E39" s="60">
+      <c r="E39" s="11">
         <v>30</v>
       </c>
-      <c r="F39" s="52" t="s">
+      <c r="F39" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="69"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="52" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="38"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="52" t="s">
+      <c r="D40" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E40" s="59">
+      <c r="E40" s="10">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F40" s="52" t="s">
+      <c r="F40" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="69"/>
-      <c r="B41" s="56"/>
-      <c r="C41" s="52" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="38"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="52" t="s">
+      <c r="D41" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="E41" s="59">
+      <c r="E41" s="10">
         <v>0.98</v>
       </c>
-      <c r="F41" s="52" t="s">
+      <c r="F41" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="69"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="52" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="38"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D42" s="52" t="s">
+      <c r="D42" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E42" s="59">
+      <c r="E42" s="10">
         <v>0.98</v>
       </c>
-      <c r="F42" s="52" t="s">
+      <c r="F42" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="69"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="52" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="38"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="52" t="s">
+      <c r="D43" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E43" s="59">
+      <c r="E43" s="10">
         <v>0.05</v>
       </c>
-      <c r="F43" s="52" t="s">
+      <c r="F43" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="69"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="55" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="38"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D44" s="55" t="s">
+      <c r="D44" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="E44" s="61">
+      <c r="E44" s="14">
         <v>0</v>
       </c>
-      <c r="F44" s="55" t="s">
+      <c r="F44" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="69"/>
-      <c r="B45" s="76" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="38"/>
+      <c r="B45" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="50" t="s">
+      <c r="D45" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="72">
+      <c r="E45" s="16">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F45" s="50" t="s">
+      <c r="F45" s="12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="69"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="38"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="52" t="s">
+      <c r="D46" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="53">
+      <c r="E46" s="8">
         <f>E47*4</f>
         <v>424</v>
       </c>
-      <c r="F46" s="52" t="s">
+      <c r="F46" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="69"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="52" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="38"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="52" t="s">
+      <c r="D47" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E47" s="53">
+      <c r="E47" s="8">
         <v>106</v>
       </c>
-      <c r="F47" s="52" t="s">
+      <c r="F47" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="69"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="52" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="38"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="52" t="s">
+      <c r="D48" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E48" s="59">
+      <c r="E48" s="10">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F48" s="52" t="s">
+      <c r="F48" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="69"/>
-      <c r="B49" s="51"/>
-      <c r="C49" s="52" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="38"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="52" t="s">
+      <c r="D49" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E49" s="59">
+      <c r="E49" s="10">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F49" s="52" t="s">
+      <c r="F49" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="69"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="52" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="38"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D50" s="52" t="s">
+      <c r="D50" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E50" s="59">
+      <c r="E50" s="10">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F50" s="52" t="s">
+      <c r="F50" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="69"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="52" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="38"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D51" s="52" t="s">
+      <c r="D51" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E51" s="53">
+      <c r="E51" s="8">
         <v>0.25</v>
       </c>
-      <c r="F51" s="52" t="s">
+      <c r="F51" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="69"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="52" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="38"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D52" s="52" t="s">
+      <c r="D52" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E52" s="59">
+      <c r="E52" s="10">
         <v>0</v>
       </c>
-      <c r="F52" s="52" t="s">
+      <c r="F52" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="69"/>
-      <c r="B53" s="51"/>
-      <c r="C53" s="52" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="38"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="52" t="s">
+      <c r="D53" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E53" s="60">
+      <c r="E53" s="11">
         <v>15</v>
       </c>
-      <c r="F53" s="52" t="s">
+      <c r="F53" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
-      <c r="B54" s="78"/>
-      <c r="C54" s="79" t="s">
+    <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="39"/>
+      <c r="B54" s="46"/>
+      <c r="C54" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D54" s="79" t="s">
+      <c r="D54" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E54" s="80">
+      <c r="E54" s="18">
         <v>0.1</v>
       </c>
-      <c r="F54" s="79" t="s">
+      <c r="F54" s="17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="66" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B55" s="81" t="s">
+      <c r="B55" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="57" t="s">
+      <c r="C55" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D55" s="57" t="s">
+      <c r="D55" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E55" s="68">
+      <c r="E55" s="7">
         <v>0.1699</v>
       </c>
-      <c r="F55" s="57" t="s">
+      <c r="F55" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="69"/>
-      <c r="B56" s="76" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="38"/>
+      <c r="B56" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C56" s="50" t="s">
+      <c r="C56" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D56" s="50" t="s">
+      <c r="D56" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E56" s="72">
+      <c r="E56" s="16">
         <v>0.99</v>
       </c>
-      <c r="F56" s="50" t="s">
+      <c r="F56" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="69"/>
-      <c r="B57" s="56"/>
-      <c r="C57" s="52" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="38"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="52" t="s">
+      <c r="D57" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E57" s="19">
         <v>1100</v>
       </c>
-      <c r="F57" s="52" t="s">
+      <c r="F57" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="69"/>
-      <c r="B58" s="56"/>
-      <c r="C58" s="52" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="38"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D58" s="52" t="s">
+      <c r="D58" s="2" t="s">
         <v>44</v>
       </c>
       <c r="E58" s="19">
         <v>17.84</v>
       </c>
-      <c r="F58" s="52" t="s">
+      <c r="F58" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="69"/>
-      <c r="B59" s="56"/>
-      <c r="C59" s="52" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="38"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D59" s="52" t="s">
+      <c r="D59" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E59" s="53">
+      <c r="E59" s="8">
         <v>0</v>
       </c>
-      <c r="F59" s="52" t="s">
+      <c r="F59" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="69"/>
-      <c r="B60" s="56"/>
-      <c r="C60" s="52" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="38"/>
+      <c r="B60" s="41"/>
+      <c r="C60" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D60" s="52" t="s">
+      <c r="D60" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E60" s="60">
+      <c r="E60" s="11">
         <v>25</v>
       </c>
-      <c r="F60" s="52" t="s">
+      <c r="F60" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="69"/>
-      <c r="B61" s="56"/>
-      <c r="C61" s="52" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="38"/>
+      <c r="B61" s="41"/>
+      <c r="C61" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="52" t="s">
+      <c r="D61" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E61" s="53">
+      <c r="E61" s="8">
         <v>1000000</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="69"/>
-      <c r="B62" s="75"/>
-      <c r="C62" s="55" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="38"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="55" t="s">
+      <c r="D62" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E62" s="61">
+      <c r="E62" s="14">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F62" s="55" t="s">
+      <c r="F62" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="69"/>
-      <c r="B63" s="76" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="38"/>
+      <c r="B63" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C63" s="50" t="s">
+      <c r="C63" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="50" t="s">
+      <c r="D63" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E63" s="72">
+      <c r="E63" s="16">
         <v>0.997</v>
       </c>
-      <c r="F63" s="50" t="s">
+      <c r="F63" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="69"/>
-      <c r="B64" s="56"/>
-      <c r="C64" s="52" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="38"/>
+      <c r="B64" s="41"/>
+      <c r="C64" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D64" s="52" t="s">
+      <c r="D64" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="19">
         <v>1080</v>
       </c>
-      <c r="F64" s="52" t="s">
+      <c r="F64" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="69"/>
-      <c r="B65" s="56"/>
-      <c r="C65" s="52" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="38"/>
+      <c r="B65" s="41"/>
+      <c r="C65" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D65" s="52" t="s">
+      <c r="D65" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E65" s="19">
         <v>12.68</v>
       </c>
-      <c r="F65" s="52" t="s">
+      <c r="F65" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="69"/>
-      <c r="B66" s="56"/>
-      <c r="C66" s="52" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="38"/>
+      <c r="B66" s="41"/>
+      <c r="C66" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D66" s="52" t="s">
+      <c r="D66" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E66" s="22">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F66" s="52" t="s">
+      <c r="F66" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="69"/>
-      <c r="B67" s="56"/>
-      <c r="C67" s="52" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="38"/>
+      <c r="B67" s="41"/>
+      <c r="C67" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D67" s="52" t="s">
+      <c r="D67" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E67" s="60">
+      <c r="E67" s="11">
         <v>25</v>
       </c>
-      <c r="F67" s="52" t="s">
+      <c r="F67" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="69"/>
-      <c r="B68" s="56"/>
-      <c r="C68" s="52" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="38"/>
+      <c r="B68" s="41"/>
+      <c r="C68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D68" s="52" t="s">
+      <c r="D68" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E68" s="82">
+      <c r="E68" s="20">
         <v>1000000</v>
       </c>
-      <c r="F68" s="52" t="s">
+      <c r="F68" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="77"/>
-      <c r="B69" s="83"/>
-      <c r="C69" s="79" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="39"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D69" s="79" t="s">
+      <c r="D69" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="E69" s="80">
+      <c r="E69" s="18">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F69" s="79" t="s">
+      <c r="F69" s="17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="66" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="B70" s="84" t="s">
+      <c r="B70" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C70" s="85" t="s">
+      <c r="C70" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="D70" s="85" t="s">
+      <c r="D70" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="E70" s="86">
-        <v>-1E-4</v>
-      </c>
-      <c r="F70" s="85" t="s">
+      <c r="E70" s="33">
+        <v>0</v>
+      </c>
+      <c r="F70" s="32" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="69"/>
-      <c r="B71" s="65" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="38"/>
+      <c r="B71" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="C71" s="52" t="s">
+      <c r="C71" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D71" s="52" t="s">
+      <c r="D71" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="E71" s="59">
-        <v>-1E-4</v>
-      </c>
-      <c r="F71" s="52" t="s">
+      <c r="E71" s="10">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="69"/>
-      <c r="B72" s="87" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="38"/>
+      <c r="B72" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="C72" s="88" t="s">
+      <c r="C72" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="88" t="s">
+      <c r="D72" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="E72" s="89">
+      <c r="E72" s="36">
         <v>-1.5</v>
       </c>
-      <c r="F72" s="88" t="s">
+      <c r="F72" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="69"/>
-      <c r="B73" s="87" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="38"/>
+      <c r="B73" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="88" t="s">
+      <c r="C73" s="35" t="s">
         <v>372</v>
       </c>
-      <c r="D73" s="88" t="s">
+      <c r="D73" s="35" t="s">
         <v>373</v>
       </c>
-      <c r="E73" s="89">
+      <c r="E73" s="36">
         <v>-0.55000000000000004</v>
       </c>
-      <c r="F73" s="88" t="s">
+      <c r="F73" s="35" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="77"/>
-      <c r="B74" s="63" t="s">
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="39"/>
+      <c r="B74" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="C74" s="79" t="s">
+      <c r="C74" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="D74" s="79" t="s">
+      <c r="D74" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="E74" s="80">
+      <c r="E74" s="18">
         <f>-2.2</f>
         <v>-2.2000000000000002</v>
       </c>
-      <c r="F74" s="79" t="s">
+      <c r="F74" s="17" t="s">
         <v>345</v>
       </c>
     </row>
@@ -3503,18 +3443,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F149"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="2"/>
+    <col min="1" max="1" width="14.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>69</v>
       </c>
@@ -3534,11 +3474,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="47" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -3552,9 +3492,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="30"/>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="38"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="2" t="s">
         <v>107</v>
       </c>
@@ -3566,9 +3506,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="30"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="38"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="2" t="s">
         <v>84</v>
       </c>
@@ -3580,9 +3520,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="30"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="38"/>
+      <c r="B5" s="45"/>
       <c r="C5" s="2" t="s">
         <v>138</v>
       </c>
@@ -3594,9 +3534,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="30"/>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="38"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="2" t="s">
         <v>141</v>
       </c>
@@ -3608,9 +3548,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="30"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="38"/>
+      <c r="B7" s="45"/>
       <c r="C7" s="2" t="s">
         <v>155</v>
       </c>
@@ -3622,9 +3562,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="30"/>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="38"/>
+      <c r="B8" s="45"/>
       <c r="C8" s="2" t="s">
         <v>196</v>
       </c>
@@ -3636,9 +3576,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="30"/>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="38"/>
+      <c r="B9" s="45"/>
       <c r="C9" s="2" t="s">
         <v>167</v>
       </c>
@@ -3650,9 +3590,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="30"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="38"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="2" t="s">
         <v>188</v>
       </c>
@@ -3664,14 +3604,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="30"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="38"/>
+      <c r="B11" s="45"/>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="35" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="38"/>
+      <c r="B12" s="56" t="s">
         <v>364</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -3685,9 +3625,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="36"/>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="38"/>
+      <c r="B13" s="51"/>
       <c r="C13" s="2" t="s">
         <v>363</v>
       </c>
@@ -3699,9 +3639,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="36"/>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="38"/>
+      <c r="B14" s="51"/>
       <c r="C14" s="2" t="s">
         <v>380</v>
       </c>
@@ -3713,9 +3653,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="36"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="38"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="2" t="s">
         <v>139</v>
       </c>
@@ -3727,9 +3667,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="36"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="38"/>
+      <c r="B16" s="51"/>
       <c r="C16" s="2" t="s">
         <v>238</v>
       </c>
@@ -3741,9 +3681,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="36"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="38"/>
+      <c r="B17" s="51"/>
       <c r="C17" s="2" t="s">
         <v>84</v>
       </c>
@@ -3755,9 +3695,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="36"/>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="38"/>
+      <c r="B18" s="51"/>
       <c r="C18" s="2" t="s">
         <v>141</v>
       </c>
@@ -3769,9 +3709,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="36"/>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="38"/>
+      <c r="B19" s="51"/>
       <c r="C19" s="2" t="s">
         <v>155</v>
       </c>
@@ -3783,9 +3723,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="36"/>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="38"/>
+      <c r="B20" s="51"/>
       <c r="C20" s="2" t="s">
         <v>196</v>
       </c>
@@ -3797,9 +3737,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="36"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="38"/>
+      <c r="B21" s="51"/>
       <c r="C21" s="2" t="s">
         <v>167</v>
       </c>
@@ -3811,9 +3751,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="36"/>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="38"/>
+      <c r="B22" s="51"/>
       <c r="C22" s="2" t="s">
         <v>188</v>
       </c>
@@ -3825,17 +3765,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="37"/>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="38"/>
+      <c r="B23" s="57"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="14"/>
       <c r="F23" s="13"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33"/>
-      <c r="B24" s="29" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="38"/>
+      <c r="B24" s="48" t="s">
         <v>262</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3849,9 +3789,9 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="30"/>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="38"/>
+      <c r="B25" s="45"/>
       <c r="C25" s="2" t="s">
         <v>107</v>
       </c>
@@ -3863,9 +3803,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="33"/>
-      <c r="B26" s="30"/>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="38"/>
+      <c r="B26" s="45"/>
       <c r="C26" s="2" t="s">
         <v>84</v>
       </c>
@@ -3877,9 +3817,9 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="33"/>
-      <c r="B27" s="30"/>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="38"/>
+      <c r="B27" s="45"/>
       <c r="C27" s="2" t="s">
         <v>283</v>
       </c>
@@ -3891,9 +3831,9 @@
         <v>282</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="30"/>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="38"/>
+      <c r="B28" s="45"/>
       <c r="C28" s="2" t="s">
         <v>141</v>
       </c>
@@ -3905,9 +3845,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="30"/>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="38"/>
+      <c r="B29" s="45"/>
       <c r="C29" s="2" t="s">
         <v>155</v>
       </c>
@@ -3919,9 +3859,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="30"/>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="38"/>
+      <c r="B30" s="45"/>
       <c r="C30" s="2" t="s">
         <v>196</v>
       </c>
@@ -3933,9 +3873,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="30"/>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="38"/>
+      <c r="B31" s="45"/>
       <c r="C31" s="2" t="s">
         <v>167</v>
       </c>
@@ -3947,9 +3887,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="30"/>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="38"/>
+      <c r="B32" s="45"/>
       <c r="C32" s="2" t="s">
         <v>188</v>
       </c>
@@ -3961,17 +3901,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="31"/>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="38"/>
+      <c r="B33" s="49"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
       <c r="E33" s="14"/>
       <c r="F33" s="13"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="33"/>
-      <c r="B34" s="28" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="38"/>
+      <c r="B34" s="41" t="s">
         <v>229</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -3985,9 +3925,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="33"/>
-      <c r="B35" s="28"/>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="38"/>
+      <c r="B35" s="41"/>
       <c r="C35" s="2" t="s">
         <v>107</v>
       </c>
@@ -3999,9 +3939,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="B36" s="28"/>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="38"/>
+      <c r="B36" s="41"/>
       <c r="C36" s="2" t="s">
         <v>84</v>
       </c>
@@ -4013,9 +3953,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="28"/>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="38"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="2" t="s">
         <v>270</v>
       </c>
@@ -4027,9 +3967,9 @@
         <v>282</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="33"/>
-      <c r="B38" s="28"/>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="38"/>
+      <c r="B38" s="41"/>
       <c r="C38" s="2" t="s">
         <v>248</v>
       </c>
@@ -4041,9 +3981,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="B39" s="28"/>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="38"/>
+      <c r="B39" s="41"/>
       <c r="C39" s="2" t="s">
         <v>141</v>
       </c>
@@ -4055,9 +3995,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="28"/>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="38"/>
+      <c r="B40" s="41"/>
       <c r="C40" s="2" t="s">
         <v>155</v>
       </c>
@@ -4069,9 +4009,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="B41" s="28"/>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="38"/>
+      <c r="B41" s="41"/>
       <c r="C41" s="2" t="s">
         <v>196</v>
       </c>
@@ -4083,9 +4023,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="28"/>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="38"/>
+      <c r="B42" s="41"/>
       <c r="C42" s="2" t="s">
         <v>167</v>
       </c>
@@ -4097,9 +4037,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="33"/>
-      <c r="B43" s="28"/>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="38"/>
+      <c r="B43" s="41"/>
       <c r="C43" s="2" t="s">
         <v>188</v>
       </c>
@@ -4111,16 +4051,16 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="33"/>
-      <c r="B44" s="28"/>
+    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="38"/>
+      <c r="B44" s="41"/>
       <c r="E44" s="10"/>
     </row>
-    <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="32" t="s">
+    <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="41" t="s">
+      <c r="B45" s="40" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -4134,9 +4074,9 @@
         <v>392</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="33"/>
-      <c r="B46" s="28"/>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="38"/>
+      <c r="B46" s="41"/>
       <c r="C46" s="2" t="s">
         <v>111</v>
       </c>
@@ -4148,9 +4088,9 @@
         <v>393</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="28"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="38"/>
+      <c r="B47" s="41"/>
       <c r="C47" s="2" t="s">
         <v>135</v>
       </c>
@@ -4162,9 +4102,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="33"/>
-      <c r="B48" s="28"/>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="38"/>
+      <c r="B48" s="41"/>
       <c r="C48" s="2" t="s">
         <v>136</v>
       </c>
@@ -4176,9 +4116,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="B49" s="28"/>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="38"/>
+      <c r="B49" s="41"/>
       <c r="C49" s="2" t="s">
         <v>141</v>
       </c>
@@ -4190,9 +4130,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="33"/>
-      <c r="B50" s="28"/>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="38"/>
+      <c r="B50" s="41"/>
       <c r="C50" s="2" t="s">
         <v>155</v>
       </c>
@@ -4204,9 +4144,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="33"/>
-      <c r="B51" s="28"/>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="38"/>
+      <c r="B51" s="41"/>
       <c r="C51" s="2" t="s">
         <v>196</v>
       </c>
@@ -4218,9 +4158,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="28"/>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="38"/>
+      <c r="B52" s="41"/>
       <c r="C52" s="2" t="s">
         <v>167</v>
       </c>
@@ -4232,9 +4172,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="33"/>
-      <c r="B53" s="28"/>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="38"/>
+      <c r="B53" s="41"/>
       <c r="C53" s="2" t="s">
         <v>188</v>
       </c>
@@ -4246,17 +4186,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="33"/>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="38"/>
       <c r="B54" s="42"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="33"/>
-      <c r="B55" s="28" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="38"/>
+      <c r="B55" s="41" t="s">
         <v>305</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -4270,9 +4210,9 @@
         <v>328</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="33"/>
-      <c r="B56" s="28"/>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="38"/>
+      <c r="B56" s="41"/>
       <c r="C56" s="2" t="s">
         <v>111</v>
       </c>
@@ -4284,9 +4224,9 @@
         <v>329</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="33"/>
-      <c r="B57" s="28"/>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="38"/>
+      <c r="B57" s="41"/>
       <c r="C57" s="2" t="s">
         <v>135</v>
       </c>
@@ -4298,9 +4238,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="B58" s="28"/>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="38"/>
+      <c r="B58" s="41"/>
       <c r="C58" s="2" t="s">
         <v>136</v>
       </c>
@@ -4312,9 +4252,9 @@
         <v>391</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="33"/>
-      <c r="B59" s="28"/>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="38"/>
+      <c r="B59" s="41"/>
       <c r="C59" s="2" t="s">
         <v>141</v>
       </c>
@@ -4326,9 +4266,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="33"/>
-      <c r="B60" s="28"/>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="38"/>
+      <c r="B60" s="41"/>
       <c r="C60" s="2" t="s">
         <v>155</v>
       </c>
@@ -4340,9 +4280,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="33"/>
-      <c r="B61" s="28"/>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="38"/>
+      <c r="B61" s="41"/>
       <c r="C61" s="2" t="s">
         <v>196</v>
       </c>
@@ -4354,9 +4294,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="33"/>
-      <c r="B62" s="28"/>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="38"/>
+      <c r="B62" s="41"/>
       <c r="C62" s="2" t="s">
         <v>167</v>
       </c>
@@ -4368,9 +4308,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="33"/>
-      <c r="B63" s="28"/>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="38"/>
+      <c r="B63" s="41"/>
       <c r="C63" s="2" t="s">
         <v>188</v>
       </c>
@@ -4382,14 +4322,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33"/>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="38"/>
       <c r="B64" s="42"/>
       <c r="E64" s="10"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="39" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="38"/>
+      <c r="B65" s="43" t="s">
         <v>6</v>
       </c>
       <c r="C65" s="12" t="s">
@@ -4403,9 +4343,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
-      <c r="B66" s="28"/>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="38"/>
+      <c r="B66" s="41"/>
       <c r="C66" s="2" t="s">
         <v>113</v>
       </c>
@@ -4417,9 +4357,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
-      <c r="B67" s="30"/>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="38"/>
+      <c r="B67" s="45"/>
       <c r="C67" s="2" t="s">
         <v>111</v>
       </c>
@@ -4431,9 +4371,9 @@
         <v>114</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
-      <c r="B68" s="30"/>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="38"/>
+      <c r="B68" s="45"/>
       <c r="C68" s="2" t="s">
         <v>107</v>
       </c>
@@ -4445,9 +4385,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="33"/>
-      <c r="B69" s="30"/>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="38"/>
+      <c r="B69" s="45"/>
       <c r="C69" s="2" t="s">
         <v>126</v>
       </c>
@@ -4459,9 +4399,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="33"/>
-      <c r="B70" s="30"/>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="38"/>
+      <c r="B70" s="45"/>
       <c r="C70" s="2" t="s">
         <v>127</v>
       </c>
@@ -4473,9 +4413,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33"/>
-      <c r="B71" s="30"/>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="38"/>
+      <c r="B71" s="45"/>
       <c r="C71" s="2" t="s">
         <v>141</v>
       </c>
@@ -4487,9 +4427,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="33"/>
-      <c r="B72" s="30"/>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="38"/>
+      <c r="B72" s="45"/>
       <c r="C72" s="2" t="s">
         <v>155</v>
       </c>
@@ -4501,9 +4441,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="33"/>
-      <c r="B73" s="30"/>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="38"/>
+      <c r="B73" s="45"/>
       <c r="C73" s="2" t="s">
         <v>196</v>
       </c>
@@ -4515,9 +4455,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="33"/>
-      <c r="B74" s="30"/>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="38"/>
+      <c r="B74" s="45"/>
       <c r="C74" s="2" t="s">
         <v>167</v>
       </c>
@@ -4529,9 +4469,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="33"/>
-      <c r="B75" s="30"/>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="38"/>
+      <c r="B75" s="45"/>
       <c r="C75" s="2" t="s">
         <v>188</v>
       </c>
@@ -4543,19 +4483,19 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="38"/>
-      <c r="B76" s="40"/>
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="39"/>
+      <c r="B76" s="46"/>
       <c r="C76" s="17"/>
       <c r="D76" s="17"/>
       <c r="E76" s="18"/>
       <c r="F76" s="17"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="32" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="34" t="s">
+      <c r="B77" s="47" t="s">
         <v>73</v>
       </c>
       <c r="C77" s="3" t="s">
@@ -4569,9 +4509,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="33"/>
-      <c r="B78" s="30"/>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="38"/>
+      <c r="B78" s="45"/>
       <c r="C78" s="2" t="s">
         <v>153</v>
       </c>
@@ -4583,14 +4523,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="33"/>
-      <c r="B79" s="31"/>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="38"/>
+      <c r="B79" s="49"/>
       <c r="E79" s="8"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="33"/>
-      <c r="B80" s="39" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="38"/>
+      <c r="B80" s="43" t="s">
         <v>4</v>
       </c>
       <c r="C80" s="12" t="s">
@@ -4604,9 +4544,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="33"/>
-      <c r="B81" s="28"/>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="38"/>
+      <c r="B81" s="41"/>
       <c r="C81" s="2" t="s">
         <v>107</v>
       </c>
@@ -4618,9 +4558,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="33"/>
-      <c r="B82" s="28"/>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="38"/>
+      <c r="B82" s="41"/>
       <c r="C82" s="2" t="s">
         <v>122</v>
       </c>
@@ -4632,9 +4572,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="33"/>
-      <c r="B83" s="28"/>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="38"/>
+      <c r="B83" s="41"/>
       <c r="C83" s="2" t="s">
         <v>141</v>
       </c>
@@ -4646,9 +4586,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="33"/>
-      <c r="B84" s="28"/>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="38"/>
+      <c r="B84" s="41"/>
       <c r="C84" s="2" t="s">
         <v>155</v>
       </c>
@@ -4660,9 +4600,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="33"/>
-      <c r="B85" s="28"/>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="38"/>
+      <c r="B85" s="41"/>
       <c r="C85" s="2" t="s">
         <v>161</v>
       </c>
@@ -4674,9 +4614,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="33"/>
-      <c r="B86" s="28"/>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="38"/>
+      <c r="B86" s="41"/>
       <c r="C86" s="2" t="s">
         <v>196</v>
       </c>
@@ -4688,9 +4628,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="33"/>
-      <c r="B87" s="28"/>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="38"/>
+      <c r="B87" s="41"/>
       <c r="C87" s="2" t="s">
         <v>167</v>
       </c>
@@ -4702,9 +4642,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="33"/>
-      <c r="B88" s="28"/>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="38"/>
+      <c r="B88" s="41"/>
       <c r="C88" s="2" t="s">
         <v>188</v>
       </c>
@@ -4716,13 +4656,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="33"/>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="38"/>
       <c r="B89" s="42"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="33"/>
-      <c r="B90" s="39" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="38"/>
+      <c r="B90" s="43" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="12" t="s">
@@ -4736,9 +4676,9 @@
         <v>98</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="33"/>
-      <c r="B91" s="28"/>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="38"/>
+      <c r="B91" s="41"/>
       <c r="C91" s="2" t="s">
         <v>108</v>
       </c>
@@ -4750,9 +4690,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="33"/>
-      <c r="B92" s="28"/>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="38"/>
+      <c r="B92" s="41"/>
       <c r="C92" s="2" t="s">
         <v>120</v>
       </c>
@@ -4764,9 +4704,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="33"/>
-      <c r="B93" s="28"/>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="38"/>
+      <c r="B93" s="41"/>
       <c r="C93" s="2" t="s">
         <v>141</v>
       </c>
@@ -4778,9 +4718,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="33"/>
-      <c r="B94" s="28"/>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="38"/>
+      <c r="B94" s="41"/>
       <c r="C94" s="2" t="s">
         <v>155</v>
       </c>
@@ -4792,9 +4732,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="33"/>
-      <c r="B95" s="28"/>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="38"/>
+      <c r="B95" s="41"/>
       <c r="C95" s="2" t="s">
         <v>161</v>
       </c>
@@ -4806,9 +4746,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="33"/>
-      <c r="B96" s="28"/>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="38"/>
+      <c r="B96" s="41"/>
       <c r="C96" s="2" t="s">
         <v>196</v>
       </c>
@@ -4820,9 +4760,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="33"/>
-      <c r="B97" s="28"/>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="38"/>
+      <c r="B97" s="41"/>
       <c r="C97" s="2" t="s">
         <v>167</v>
       </c>
@@ -4834,9 +4774,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="33"/>
-      <c r="B98" s="28"/>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="38"/>
+      <c r="B98" s="41"/>
       <c r="C98" s="2" t="s">
         <v>188</v>
       </c>
@@ -4848,15 +4788,15 @@
         <v>149</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="38"/>
+    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="39"/>
       <c r="B99" s="44"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="32" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="B100" s="34" t="s">
+      <c r="B100" s="47" t="s">
         <v>73</v>
       </c>
       <c r="C100" s="3" t="s">
@@ -4870,9 +4810,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="33"/>
-      <c r="B101" s="30"/>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="38"/>
+      <c r="B101" s="45"/>
       <c r="C101" s="2" t="s">
         <v>228</v>
       </c>
@@ -4884,9 +4824,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="33"/>
-      <c r="B102" s="30"/>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="38"/>
+      <c r="B102" s="45"/>
       <c r="C102" s="2" t="s">
         <v>150</v>
       </c>
@@ -4898,17 +4838,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="33"/>
-      <c r="B103" s="31"/>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="38"/>
+      <c r="B103" s="49"/>
       <c r="C103" s="13"/>
       <c r="D103" s="13"/>
       <c r="E103" s="14"/>
       <c r="F103" s="13"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="33"/>
-      <c r="B104" s="29" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="38"/>
+      <c r="B104" s="48" t="s">
         <v>292</v>
       </c>
       <c r="C104" s="2" t="s">
@@ -4922,9 +4862,9 @@
         <v>282</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="33"/>
-      <c r="B105" s="30"/>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="38"/>
+      <c r="B105" s="45"/>
       <c r="C105" s="2" t="s">
         <v>297</v>
       </c>
@@ -4936,9 +4876,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="33"/>
-      <c r="B106" s="30"/>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="38"/>
+      <c r="B106" s="45"/>
       <c r="C106" s="2" t="s">
         <v>298</v>
       </c>
@@ -4950,14 +4890,14 @@
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="33"/>
-      <c r="B107" s="31"/>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="38"/>
+      <c r="B107" s="49"/>
       <c r="E107" s="10"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="33"/>
-      <c r="B108" s="29" t="s">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="38"/>
+      <c r="B108" s="48" t="s">
         <v>79</v>
       </c>
       <c r="C108" s="12" t="s">
@@ -4971,9 +4911,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="33"/>
-      <c r="B109" s="30"/>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="38"/>
+      <c r="B109" s="45"/>
       <c r="C109" s="2" t="s">
         <v>151</v>
       </c>
@@ -4985,17 +4925,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="33"/>
-      <c r="B110" s="31"/>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="38"/>
+      <c r="B110" s="49"/>
       <c r="C110" s="13"/>
       <c r="D110" s="13"/>
       <c r="E110" s="14"/>
       <c r="F110" s="13"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="33"/>
-      <c r="B111" s="45" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="38"/>
+      <c r="B111" s="53" t="s">
         <v>371</v>
       </c>
       <c r="C111" s="12" t="s">
@@ -5009,9 +4949,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="33"/>
-      <c r="B112" s="46"/>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="38"/>
+      <c r="B112" s="54"/>
       <c r="C112" s="2" t="s">
         <v>376</v>
       </c>
@@ -5023,17 +4963,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="33"/>
-      <c r="B113" s="47"/>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="38"/>
+      <c r="B113" s="55"/>
       <c r="C113" s="13"/>
       <c r="D113" s="13"/>
       <c r="E113" s="14"/>
       <c r="F113" s="13"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="33"/>
-      <c r="B114" s="36" t="s">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="38"/>
+      <c r="B114" s="51" t="s">
         <v>331</v>
       </c>
       <c r="C114" s="2" t="s">
@@ -5047,9 +4987,9 @@
         <v>358</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="33"/>
-      <c r="B115" s="36"/>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="38"/>
+      <c r="B115" s="51"/>
       <c r="C115" s="2" t="s">
         <v>362</v>
       </c>
@@ -5061,19 +5001,19 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="38"/>
-      <c r="B116" s="43"/>
+    <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="39"/>
+      <c r="B116" s="52"/>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
       <c r="E116" s="18"/>
       <c r="F116" s="17"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="32" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A117" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="B117" s="34" t="s">
+      <c r="B117" s="47" t="s">
         <v>13</v>
       </c>
       <c r="C117" s="3" t="s">
@@ -5087,9 +5027,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="33"/>
-      <c r="B118" s="30"/>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A118" s="38"/>
+      <c r="B118" s="45"/>
       <c r="C118" s="2" t="s">
         <v>174</v>
       </c>
@@ -5100,17 +5040,17 @@
         <v>140</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="33"/>
-      <c r="B119" s="31"/>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A119" s="38"/>
+      <c r="B119" s="49"/>
       <c r="C119" s="13"/>
       <c r="D119" s="13"/>
       <c r="E119" s="13"/>
       <c r="F119" s="13"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="33"/>
-      <c r="B120" s="29" t="s">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120" s="38"/>
+      <c r="B120" s="48" t="s">
         <v>183</v>
       </c>
       <c r="C120" s="2" t="s">
@@ -5123,9 +5063,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="33"/>
-      <c r="B121" s="30"/>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121" s="38"/>
+      <c r="B121" s="45"/>
       <c r="C121" s="2" t="s">
         <v>181</v>
       </c>
@@ -5136,9 +5076,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="33"/>
-      <c r="B122" s="30"/>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" s="38"/>
+      <c r="B122" s="45"/>
       <c r="C122" s="2" t="s">
         <v>177</v>
       </c>
@@ -5149,9 +5089,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="33"/>
-      <c r="B123" s="30"/>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" s="38"/>
+      <c r="B123" s="45"/>
       <c r="C123" s="2" t="s">
         <v>179</v>
       </c>
@@ -5162,9 +5102,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="33"/>
-      <c r="B124" s="30"/>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" s="38"/>
+      <c r="B124" s="45"/>
       <c r="C124" s="2" t="s">
         <v>182</v>
       </c>
@@ -5175,9 +5115,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="33"/>
-      <c r="B125" s="30"/>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" s="38"/>
+      <c r="B125" s="45"/>
       <c r="C125" s="2" t="s">
         <v>191</v>
       </c>
@@ -5188,13 +5128,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="33"/>
-      <c r="B126" s="31"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="33"/>
-      <c r="B127" s="29" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="38"/>
+      <c r="B126" s="49"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" s="38"/>
+      <c r="B127" s="48" t="s">
         <v>206</v>
       </c>
       <c r="C127" s="12" t="s">
@@ -5208,9 +5148,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="33"/>
-      <c r="B128" s="30"/>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" s="38"/>
+      <c r="B128" s="45"/>
       <c r="C128" s="2" t="s">
         <v>204</v>
       </c>
@@ -5221,9 +5161,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="33"/>
-      <c r="B129" s="30"/>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" s="38"/>
+      <c r="B129" s="45"/>
       <c r="C129" s="2" t="s">
         <v>215</v>
       </c>
@@ -5234,9 +5174,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="33"/>
-      <c r="B130" s="30"/>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" s="38"/>
+      <c r="B130" s="45"/>
       <c r="C130" s="2" t="s">
         <v>205</v>
       </c>
@@ -5247,9 +5187,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="33"/>
-      <c r="B131" s="30"/>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" s="38"/>
+      <c r="B131" s="45"/>
       <c r="C131" s="2" t="s">
         <v>300</v>
       </c>
@@ -5260,9 +5200,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="33"/>
-      <c r="B132" s="30"/>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" s="38"/>
+      <c r="B132" s="45"/>
       <c r="C132" s="21" t="s">
         <v>324</v>
       </c>
@@ -5274,9 +5214,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="33"/>
-      <c r="B133" s="30"/>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" s="38"/>
+      <c r="B133" s="45"/>
       <c r="C133" s="21" t="s">
         <v>326</v>
       </c>
@@ -5288,9 +5228,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="33"/>
-      <c r="B134" s="30"/>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" s="38"/>
+      <c r="B134" s="45"/>
       <c r="C134" s="2" t="s">
         <v>217</v>
       </c>
@@ -5301,9 +5241,9 @@
         <v>218</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="33"/>
-      <c r="B135" s="30"/>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" s="38"/>
+      <c r="B135" s="45"/>
       <c r="C135" s="2" t="s">
         <v>221</v>
       </c>
@@ -5314,9 +5254,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="33"/>
-      <c r="B136" s="30"/>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" s="38"/>
+      <c r="B136" s="45"/>
       <c r="C136" s="2" t="s">
         <v>202</v>
       </c>
@@ -5327,9 +5267,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="33"/>
-      <c r="B137" s="30"/>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A137" s="38"/>
+      <c r="B137" s="45"/>
       <c r="C137" s="21" t="s">
         <v>249</v>
       </c>
@@ -5341,9 +5281,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="33"/>
-      <c r="B138" s="30"/>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A138" s="38"/>
+      <c r="B138" s="45"/>
       <c r="C138" s="21" t="s">
         <v>383</v>
       </c>
@@ -5355,9 +5295,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="33"/>
-      <c r="B139" s="30"/>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A139" s="38"/>
+      <c r="B139" s="45"/>
       <c r="C139" s="21" t="s">
         <v>365</v>
       </c>
@@ -5369,9 +5309,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="33"/>
-      <c r="B140" s="30"/>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A140" s="38"/>
+      <c r="B140" s="45"/>
       <c r="C140" s="21" t="s">
         <v>385</v>
       </c>
@@ -5383,17 +5323,17 @@
         <v>213</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="33"/>
-      <c r="B141" s="31"/>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A141" s="38"/>
+      <c r="B141" s="49"/>
       <c r="C141" s="21"/>
       <c r="D141" s="21"/>
       <c r="E141" s="21"/>
       <c r="F141" s="21"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="33"/>
-      <c r="B142" s="29" t="s">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A142" s="38"/>
+      <c r="B142" s="48" t="s">
         <v>222</v>
       </c>
       <c r="C142" s="12" t="s">
@@ -5407,9 +5347,9 @@
         <v>208</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="33"/>
-      <c r="B143" s="30"/>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" s="38"/>
+      <c r="B143" s="45"/>
       <c r="C143" s="2" t="s">
         <v>302</v>
       </c>
@@ -5420,9 +5360,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="33"/>
-      <c r="B144" s="30"/>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A144" s="38"/>
+      <c r="B144" s="45"/>
       <c r="C144" s="2" t="s">
         <v>225</v>
       </c>
@@ -5433,9 +5373,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="33"/>
-      <c r="B145" s="30"/>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A145" s="38"/>
+      <c r="B145" s="45"/>
       <c r="C145" s="21" t="s">
         <v>251</v>
       </c>
@@ -5447,9 +5387,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="33"/>
-      <c r="B146" s="30"/>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A146" s="38"/>
+      <c r="B146" s="45"/>
       <c r="C146" s="21" t="s">
         <v>366</v>
       </c>
@@ -5461,17 +5401,17 @@
         <v>213</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="33"/>
-      <c r="B147" s="31"/>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" s="38"/>
+      <c r="B147" s="49"/>
       <c r="C147" s="13"/>
       <c r="D147" s="13"/>
       <c r="E147" s="13"/>
       <c r="F147" s="13"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="33"/>
-      <c r="B148" s="48" t="s">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" s="38"/>
+      <c r="B148" s="50" t="s">
         <v>386</v>
       </c>
       <c r="C148" s="2" t="s">
@@ -5484,9 +5424,9 @@
         <v>345</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="33"/>
-      <c r="B149" s="48"/>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" s="38"/>
+      <c r="B149" s="50"/>
       <c r="C149" s="2" t="s">
         <v>388</v>
       </c>
@@ -5499,12 +5439,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A117:A149"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="A2:A44"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="B34:B44"/>
+    <mergeCell ref="A45:A76"/>
+    <mergeCell ref="B65:B76"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B45:B54"/>
+    <mergeCell ref="B55:B64"/>
     <mergeCell ref="B114:B116"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A77:A99"/>
@@ -5515,15 +5458,12 @@
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="B34:B44"/>
-    <mergeCell ref="A45:A76"/>
-    <mergeCell ref="B65:B76"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B45:B54"/>
-    <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A117:A149"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="B120:B126"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5533,57 +5473,57 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C614C4-2B7C-4798-B4E2-788104541F45}">
   <dimension ref="B1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" style="23"/>
+    <col min="2" max="2" width="11.54296875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B1" s="23" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="23" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B22" s="26" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="23" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" s="23" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B27" s="23" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" s="23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="24" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" s="25" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B31" s="25"/>
     </row>
   </sheetData>
